--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_43_R5.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_43_R5.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.2888</v>
+        <v>9.1145</v>
       </c>
       <c r="E2" t="n">
-        <v>11.0403</v>
+        <v>11.8659</v>
       </c>
       <c r="F2" t="n">
         <v>-2.7515</v>
@@ -610,10 +610,10 @@
         <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2265</v>
+        <v>-0.4009</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8883</v>
+        <v>-0.0626</v>
       </c>
       <c r="U2" t="n">
         <v>-0.3383</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. HOARD</t>
+          <t>T. LEAF</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9636</v>
+        <v>1.7741</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1188</v>
+        <v>2.0309</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1552</v>
+        <v>-0.2569</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.6186</v>
+        <v>-1.4412</v>
       </c>
       <c r="H3" t="n">
-        <v>-4.5992</v>
+        <v>-2.7528</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9805</v>
+        <v>1.3117</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9408</v>
+        <v>-0.4935</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.8241</v>
+        <v>-1.2296</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8833</v>
+        <v>0.7361</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.6778</v>
+        <v>-0.9477</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.775</v>
+        <v>-1.5232</v>
       </c>
       <c r="O3" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.5756</v>
       </c>
       <c r="P3" t="n">
-        <v>3.7112</v>
+        <v>0.9278</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.7112</v>
+        <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2653</v>
+        <v>0.6792</v>
       </c>
       <c r="T3" t="n">
-        <v>3.3817</v>
+        <v>0.9162</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1164</v>
+        <v>-0.237</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3943</v>
+        <v>1.6083</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6778999999999999</v>
+        <v>1.6083</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. LEAF</t>
+          <t>J. HOARD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3974</v>
+        <v>0.5545</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6207</v>
+        <v>0.8777</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2233</v>
+        <v>-0.3232</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.4412</v>
+        <v>-3.6186</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.7528</v>
+        <v>-4.5992</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3117</v>
+        <v>0.9805</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4935</v>
+        <v>-0.9408</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.2296</v>
+        <v>-1.8241</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7361</v>
+        <v>0.8833</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9477</v>
+        <v>-2.6778</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5232</v>
+        <v>-2.775</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5756</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9278</v>
+        <v>3.7112</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9278</v>
+        <v>3.7112</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3025</v>
+        <v>0.8562</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5059</v>
+        <v>1.1406</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2034</v>
+        <v>-0.2844</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6083</v>
+        <v>-0.3943</v>
       </c>
       <c r="W4" t="n">
-        <v>1.6083</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3742</v>
+        <v>0.1984</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2216</v>
+        <v>0.6935</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5958</v>
+        <v>-0.495</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4572</v>
@@ -844,13 +844,13 @@
         <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6128</v>
+        <v>-0.0402</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8136</v>
+        <v>-0.3418</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2008</v>
+        <v>0.3016</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. BRISSETT</t>
+          <t>J. DIBARTOLOMEO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7719</v>
+        <v>-0.6414</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5007</v>
+        <v>1.2341</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2713</v>
+        <v>-1.8755</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.1372</v>
+        <v>-0.2936</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1139</v>
+        <v>-1.294</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0234</v>
+        <v>1.0004</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8041</v>
+        <v>1.1043</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9782</v>
+        <v>0.0504</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1741</v>
+        <v>1.0539</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9413</v>
+        <v>-1.3979</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.0921</v>
+        <v>-1.3444</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1507</v>
+        <v>-0.0535</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3195</v>
+        <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5793</v>
+        <v>0.0286</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0148</v>
+        <v>0.1298</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5645</v>
+        <v>-0.1013</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. DIBARTOLOMEO</t>
+          <t>W. RAYMAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0288</v>
+        <v>-1.4023</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8803</v>
+        <v>-0.1326</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.9091</v>
+        <v>-1.2697</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2936</v>
+        <v>-0.4048</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.294</v>
+        <v>0.1741</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0004</v>
+        <v>-0.5788</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1043</v>
+        <v>0.0168</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0504</v>
+        <v>0.0168</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0539</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3979</v>
+        <v>-0.4216</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3444</v>
+        <v>0.1573</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0535</v>
+        <v>-0.5788</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3589</v>
+        <v>-0.1573</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.224</v>
+        <v>-0.1494</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1349</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>-1.0722</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W. RAYMAN</t>
+          <t>O. BRISSETT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2678</v>
+        <v>-2.136</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1326</v>
+        <v>-1.5622</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1353</v>
+        <v>-0.5738</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4048</v>
+        <v>-1.1372</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1741</v>
+        <v>-1.1139</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5788</v>
+        <v>-0.0234</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0168</v>
+        <v>0.8041</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0168</v>
+        <v>0.9782</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.1741</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4216</v>
+        <v>-1.9413</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1573</v>
+        <v>-2.0921</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5788</v>
+        <v>0.1507</v>
       </c>
       <c r="P8" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>0.232</v>
+        <v>2.3195</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0228</v>
+        <v>0.2153</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1494</v>
+        <v>-0.0468</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1265</v>
+        <v>0.2621</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CLARK III</t>
+          <t>T. BLATT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9513</v>
+        <v>-2.3071</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9825</v>
+        <v>-3.2096</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9689</v>
+        <v>0.9025</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5172</v>
+        <v>-1.3153</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8618</v>
+        <v>-0.0371</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.379</v>
+        <v>-1.2783</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1376</v>
+        <v>-0.6897</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3983</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.5359</v>
+        <v>-1.3787</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3796</v>
+        <v>-0.6256</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5365</v>
+        <v>-0.7261</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8431</v>
+        <v>0.1005</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4639</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5759</v>
+        <v>-0.0639</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2908</v>
+        <v>-0.2003</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2851</v>
+        <v>0.1364</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. BLATT</t>
+          <t>J. CLARK III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0141</v>
+        <v>-2.3115</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6814</v>
+        <v>-1.5107</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6673</v>
+        <v>-0.8008</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3153</v>
+        <v>-1.5172</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0371</v>
+        <v>0.8618</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2783</v>
+        <v>-2.379</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6897</v>
+        <v>-0.1376</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6889999999999999</v>
+        <v>1.3983</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3787</v>
+        <v>-1.5359</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6256</v>
+        <v>-1.3796</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7261</v>
+        <v>-0.5365</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1005</v>
+        <v>-0.8431</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.771</v>
+        <v>0.0639</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6721</v>
+        <v>0.181</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0988</v>
+        <v>-0.1171</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6257</v>
+        <v>-3.2883</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4835</v>
+        <v>-2.0117</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1422</v>
+        <v>-1.2766</v>
       </c>
       <c r="G11" t="n">
         <v>-0.6698</v>
@@ -1312,13 +1312,13 @@
         <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9586</v>
+        <v>-0.6212</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6721</v>
+        <v>-0.2003</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2864</v>
+        <v>-0.4208</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1418</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6034</v>
+        <v>-3.5425</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.7499</v>
+        <v>-3.9243</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1465</v>
+        <v>0.3818</v>
       </c>
       <c r="G12" t="n">
         <v>-2.9541</v>
@@ -1390,13 +1390,13 @@
         <v>2.7834</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9149</v>
+        <v>-0.854</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3443</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5706</v>
+        <v>-0.3354</v>
       </c>
       <c r="V12" t="n">
         <v>0.9615</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.987399999999999</v>
+        <v>-3.9876</v>
       </c>
       <c r="E13" t="n">
-        <v>4.351100000000001</v>
+        <v>4.350999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.338800000000001</v>
+        <v>-8.338699999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-6.0771</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.9174</v>
+        <v>-7.917400000000002</v>
       </c>
       <c r="I13" t="n">
         <v>1.8402</v>
@@ -1447,7 +1447,7 @@
         <v>6.8521</v>
       </c>
       <c r="L13" t="n">
-        <v>5.034700000000001</v>
+        <v>5.034700000000003</v>
       </c>
       <c r="M13" t="n">
         <v>-17.9638</v>
@@ -1468,10 +1468,10 @@
         <v>18.5562</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2943</v>
+        <v>-0.2942999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8477999999999999</v>
+        <v>0.8478000000000001</v>
       </c>
       <c r="U13" t="n">
         <v>-1.1421</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. MILUTINOV</t>
+          <t>S. VEZENKOV</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.7524</v>
+        <v>6.6138</v>
       </c>
       <c r="E14" t="n">
-        <v>10.1792</v>
+        <v>5.5898</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.4268</v>
+        <v>1.024</v>
       </c>
       <c r="G14" t="n">
-        <v>3.4577</v>
+        <v>2.7801</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5579</v>
+        <v>1.8967</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1002</v>
+        <v>0.8833</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1903</v>
+        <v>3.7778</v>
       </c>
       <c r="K14" t="n">
-        <v>3.9695</v>
+        <v>3.0452</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2208</v>
+        <v>0.7326</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7326</v>
+        <v>-0.9977</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4116</v>
+        <v>-1.1484</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3211</v>
+        <v>0.1507</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5989</v>
+        <v>0.9935</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6305</v>
+        <v>0.2912</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0316</v>
+        <v>0.7022</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5361</v>
+        <v>2.1444</v>
       </c>
       <c r="W14" t="n">
-        <v>3.3584</v>
+        <v>2.6805</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.8223</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. VEZENKOV</t>
+          <t>N. MILUTINOV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.2181</v>
+        <v>6.3192</v>
       </c>
       <c r="E15" t="n">
-        <v>5.3539</v>
+        <v>8.4099</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8642</v>
+        <v>-2.0907</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7801</v>
+        <v>3.4577</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8967</v>
+        <v>3.5579</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8833</v>
+        <v>-0.1002</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7778</v>
+        <v>4.1903</v>
       </c>
       <c r="K15" t="n">
-        <v>3.0452</v>
+        <v>3.9695</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7326</v>
+        <v>0.2208</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9977</v>
+        <v>-0.7326</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1484</v>
+        <v>-0.4116</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1507</v>
+        <v>-0.3211</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5977</v>
+        <v>1.1657</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0553</v>
+        <v>0.8612</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5424</v>
+        <v>0.3044</v>
       </c>
       <c r="V15" t="n">
-        <v>2.1444</v>
+        <v>0.5361</v>
       </c>
       <c r="W15" t="n">
-        <v>2.6805</v>
+        <v>3.3584</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5361</v>
+        <v>-2.8223</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>T. WARD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4093</v>
+        <v>2.0844</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6055</v>
+        <v>0.2627</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1962</v>
+        <v>1.8217</v>
       </c>
       <c r="G16" t="n">
-        <v>1.457</v>
+        <v>0.8714</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0324</v>
+        <v>-0.8751</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5754</v>
+        <v>1.7465</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1017</v>
+        <v>1.3829</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9913</v>
+        <v>0.2086</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1104</v>
+        <v>1.1742</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6447</v>
+        <v>-0.5115</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9588</v>
+        <v>-1.0838</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6859</v>
+        <v>0.5723</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0244</v>
+        <v>0.1228</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0578</v>
+        <v>0.0395</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0334</v>
+        <v>0.0833</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5361</v>
+        <v>0.3943</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1418</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. WARD</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4445</v>
+        <v>1.3376</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2091</v>
+        <v>1.7798</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6537</v>
+        <v>-0.4422</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8714</v>
+        <v>1.457</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8751</v>
+        <v>2.0324</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7465</v>
+        <v>-0.5754</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3829</v>
+        <v>3.1017</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2086</v>
+        <v>2.9913</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1742</v>
+        <v>0.1104</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5115</v>
+        <v>-1.6447</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0838</v>
+        <v>-0.9588</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5723</v>
+        <v>-0.6859</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5171</v>
+        <v>-0.0472</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4323</v>
+        <v>0.2322</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0848</v>
+        <v>-0.2794</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3943</v>
+        <v>-0.5361</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3943</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.639</v>
+        <v>0.0674</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3485</v>
+        <v>1.5844</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9875</v>
+        <v>-1.517</v>
       </c>
       <c r="G18" t="n">
         <v>0.5033</v>
@@ -1858,13 +1858,13 @@
         <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3021</v>
+        <v>-0.5957</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3576</v>
+        <v>-0.1217</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9445</v>
+        <v>-0.474</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5361</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5365</v>
+        <v>-0.9746</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3568</v>
+        <v>0.115</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1797</v>
+        <v>-1.0896</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4654</v>
@@ -1936,13 +1936,13 @@
         <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8391</v>
+        <v>-0.2772</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5975</v>
+        <v>-0.1256</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2416</v>
+        <v>-0.1516</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. LARENTZAKIS</t>
+          <t>T. DORSEY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1321</v>
+        <v>-2.0429</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7562</v>
+        <v>-2.7754</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3759</v>
+        <v>0.7325</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2263</v>
+        <v>-0.9486</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0552</v>
+        <v>1.3</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1711</v>
+        <v>-2.2486</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4471</v>
+        <v>0.6495</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3025</v>
+        <v>2.3127</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-1.6633</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7792</v>
+        <v>-1.5981</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3577</v>
+        <v>-1.0127</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4216</v>
+        <v>-0.5854</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9278</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>-4.639</v>
       </c>
       <c r="R20" t="n">
-        <v>0.232</v>
+        <v>2.5515</v>
       </c>
       <c r="S20" t="n">
-        <v>0.022</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1494</v>
+        <v>0.1419</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1713</v>
+        <v>-0.0791</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.9304</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. DORSEY</t>
+          <t>G. LARENTZAKIS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4361</v>
+        <v>-2.0814</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0113</v>
+        <v>-1.6382</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5752</v>
+        <v>-0.4432</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9486</v>
+        <v>-1.2263</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3</v>
+        <v>-0.0552</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.2486</v>
+        <v>-1.1711</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6495</v>
+        <v>-0.4471</v>
       </c>
       <c r="K21" t="n">
-        <v>2.3127</v>
+        <v>0.3025</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.6633</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5981</v>
+        <v>-0.7792</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0127</v>
+        <v>-0.3577</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5854</v>
+        <v>-0.4216</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.0876</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.639</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>2.5515</v>
+        <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3304</v>
+        <v>0.0727</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.094</v>
+        <v>-0.0314</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2363</v>
+        <v>0.1041</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9304</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. PETERS</t>
+          <t>S. LEE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7797</v>
+        <v>-3.1459</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.766</v>
+        <v>-2.3411</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0137</v>
+        <v>-0.8048</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.5274</v>
+        <v>1.1753</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3697</v>
+        <v>-0.0358</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1577</v>
+        <v>1.2112</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1478</v>
+        <v>2.2624</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1478</v>
+        <v>0.8907</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.3717</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3796</v>
+        <v>-1.087</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.222</v>
+        <v>-0.9265</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1577</v>
+        <v>-0.1605</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.3917</v>
+        <v>-3.7112</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3195</v>
+        <v>-4.639</v>
       </c>
       <c r="R22" t="n">
         <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8606</v>
+        <v>0.0679</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2987</v>
+        <v>0.0356</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5619</v>
+        <v>0.0323</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. LEE</t>
+          <t>A. PETERS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3133</v>
+        <v>-3.4036</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0488</v>
+        <v>-2.648</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2645</v>
+        <v>-0.7556</v>
       </c>
       <c r="G23" t="n">
-        <v>1.1753</v>
+        <v>-1.5274</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0358</v>
+        <v>-0.3697</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2112</v>
+        <v>-1.1577</v>
       </c>
       <c r="J23" t="n">
-        <v>2.2624</v>
+        <v>-0.1478</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8907</v>
+        <v>-0.1478</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3717</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.087</v>
+        <v>-1.3796</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9265</v>
+        <v>-0.222</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1605</v>
+        <v>-1.1577</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.7112</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.639</v>
+        <v>-2.3195</v>
       </c>
       <c r="R23" t="n">
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0996</v>
+        <v>-0.4845</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6721</v>
+        <v>-0.1808</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4274</v>
+        <v>-0.3038</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>3.9876</v>
+        <v>4.774000000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>8.338900000000001</v>
+        <v>8.338900000000002</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.3512</v>
+        <v>-3.5649</v>
       </c>
       <c r="G24" t="n">
         <v>6.0771</v>
@@ -2326,13 +2326,13 @@
         <v>13.9172</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2940999999999998</v>
+        <v>1.0808</v>
       </c>
       <c r="T24" t="n">
-        <v>1.142</v>
+        <v>1.1421</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8478</v>
+        <v>-0.06159999999999971</v>
       </c>
       <c r="V24" t="n">
         <v>2.255100000000001</v>
